--- a/filter_master_2VRDS.xlsx
+++ b/filter_master_2VRDS.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D1"/>
+  <dimension ref="A1:E2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -449,6 +449,30 @@
           <t>가스켓재고</t>
         </is>
       </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>가스켓사양</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>4B/L</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>F7701</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>7</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/filter_master_2VRDS.xlsx
+++ b/filter_master_2VRDS.xlsx
@@ -470,7 +470,7 @@
         <v>7</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E2" t="inlineStr"/>
     </row>

--- a/filter_master_2VRDS.xlsx
+++ b/filter_master_2VRDS.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:E1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -455,25 +455,6 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>4B/L</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>F7701</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
-        <v>7</v>
-      </c>
-      <c r="D2" t="n">
-        <v>3</v>
-      </c>
-      <c r="E2" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/filter_master_2VRDS.xlsx
+++ b/filter_master_2VRDS.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1"/>
+  <dimension ref="A1:E2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -454,6 +454,25 @@
           <t>가스켓사양</t>
         </is>
       </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>4B/L</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>F7702B</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>8</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
